--- a/epsilon-phi-core/proposal-tool/dataTemplates/ProposalTool_DataTemplates.xlsx
+++ b/epsilon-phi-core/proposal-tool/dataTemplates/ProposalTool_DataTemplates.xlsx
@@ -288,41 +288,47 @@
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
+        <t>ShareClass (optional, text)
+Dis (distributing) or Acc (accumulating), and nothing else - a typo is refused on load. Leave blank, or drop the column, for a product that has no share class.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
         <t>Source (yes, text)
 Free text, e.g. Internal, External. A doughnut axis.</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="I1" authorId="0" shapeId="0">
       <text>
         <t>Liquidity (yes, text)
 Free text, e.g. Daily, Quarterly. A doughnut axis.</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="J1" authorId="0" shapeId="0">
       <text>
         <t>ExposureCurrency (yes, text)
 Free text, e.g. USD. A doughnut axis.</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="K1" authorId="0" shapeId="0">
       <text>
         <t>ProductCost (yes, number &gt;= 0)
 A PERCENT: 0.25 means 0.25%. Not a fraction.</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="L1" authorId="0" shapeId="0">
       <text>
         <t>FeeGroup (yes, text)
 One of the fee groups on the Valid values sheet. The set is defined by the feeRates sheet, so the two must agree.</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="M1" authorId="0" shapeId="0">
       <text>
         <t>DistributionYield (optional, number &gt;= 0)
 A PERCENT. Leave blank, or drop the column, if there is none.</t>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="N1" authorId="0" shapeId="0">
       <text>
         <t>MinimumInvestment (optional, number &gt;= 0)
 CURRENCY UNITS: 5000000 means $5m. Blank means no minimum. THIS BLOCKS THE EXPORT: a position below its product minimum refuses the download, so get these right.</t>
@@ -405,7 +411,7 @@
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <t>tierMax (no, number)
-Upper edge, CURRENCY UNITS, exclusive. BLANK means open-ended.</t>
+Upper edge, CURRENCY UNITS, exclusive. LEAVE IT EMPTY ON THE TOP TIER: an empty cell is how a tier says "and up", and the tier then reads as "$100m and up". Do not write Infinity, inf, or a very large number - all three are refused on load.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
@@ -1299,7 +1305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1594,12 +1600,12 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Source</t>
+          <t>ShareClass</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1609,7 +1615,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Free text, e.g. Internal, External. A doughnut axis.</t>
+          <t>Dis (distributing) or Acc (accumulating), and nothing else - a typo is refused on load. Leave blank, or drop the column, for a product that has no share class.</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1627,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Liquidity</t>
+          <t>Source</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -1636,7 +1642,7 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t>Free text, e.g. Daily, Quarterly. A doughnut axis.</t>
+          <t>Free text, e.g. Internal, External. A doughnut axis.</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1654,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>ExposureCurrency</t>
+          <t>Liquidity</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -1663,7 +1669,7 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>Free text, e.g. USD. A doughnut axis.</t>
+          <t>Free text, e.g. Daily, Quarterly. A doughnut axis.</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1681,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>ProductCost</t>
+          <t>ExposureCurrency</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -1685,12 +1691,12 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>number &gt;= 0</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t>A PERCENT: 0.25 means 0.25%. Not a fraction.</t>
+          <t>Free text, e.g. USD. A doughnut axis.</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1708,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>FeeGroup</t>
+          <t>ProductCost</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -1712,12 +1718,12 @@
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number &gt;= 0</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>One of the fee groups on the Valid values sheet. The set is defined by the feeRates sheet, so the two must agree.</t>
+          <t>A PERCENT: 0.25 means 0.25%. Not a fraction.</t>
         </is>
       </c>
     </row>
@@ -1729,22 +1735,22 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>DistributionYield</t>
+          <t>FeeGroup</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>number &gt;= 0</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>A PERCENT. Leave blank, or drop the column, if there is none.</t>
+          <t>One of the fee groups on the Valid values sheet. The set is defined by the feeRates sheet, so the two must agree.</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1762,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>MinimumInvestment</t>
+          <t>DistributionYield</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1771,34 +1777,34 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>CURRENCY UNITS: 5000000 means $5m. Blank means no minimum. THIS BLOCKS THE EXPORT: a position below its product minimum refuses the download, so get these right.</t>
+          <t>A PERCENT. Leave blank, or drop the column, if there is none.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>sleeves</t>
+          <t>products</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Variant</t>
+          <t>MinimumInvestment</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number &gt;= 0</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>One of the four implementation types on the Valid values sheet.</t>
+          <t>CURRENCY UNITS: 5000000 means $5m. Blank means no minimum. THIS BLOCKS THE EXPORT: a position below its product minimum refuses the download, so get these right.</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1816,7 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>Variant</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -1825,7 +1831,7 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>One of the seven sleeve categories on the Valid values sheet. Private Equity and Other Private Assets share the one combined category.</t>
+          <t>One of the four implementation types on the Valid values sheet.</t>
         </is>
       </c>
     </row>
@@ -1837,7 +1843,7 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Sleeve</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
@@ -1847,12 +1853,12 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>text (&lt;= 80)</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>The sleeve name. Unique within a variant and category.</t>
+          <t>One of the seven sleeve categories on the Valid values sheet. Private Equity and Other Private Assets share the one combined category.</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1870,7 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>ProductId</t>
+          <t>Sleeve</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -1874,12 +1880,12 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>text (&lt;= 80)</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>Must exist in the products sheet.</t>
+          <t>The sleeve name. Unique within a variant and category.</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1897,7 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>Weight</t>
+          <t>ProductId</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -1901,24 +1907,24 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>A FRACTION. One sleeve's rows must sum to 1 within 0.000001.</t>
+          <t>Must exist in the products sheet.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
-          <t>feeRates</t>
+          <t>sleeves</t>
         </is>
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>schedule</t>
+          <t>Weight</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1928,12 +1934,12 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>CASP (one rate for all) or RDR (a rate per fee group).</t>
+          <t>A FRACTION. One sleeve's rows must sum to 1 within 0.000001.</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1951,12 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>feeGroup</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>yes for RDR</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
@@ -1960,7 +1966,7 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>Blank for CASP. For RDR, the fee group. The distinct values here DEFINE the set the products sheet must use.</t>
+          <t>CASP (one rate for all) or RDR (a rate per fee group).</t>
         </is>
       </c>
     </row>
@@ -1972,12 +1978,12 @@
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>tier</t>
+          <t>feeGroup</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes for RDR</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1987,7 +1993,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Tier id, e.g. T1. Every row of a tier must carry the same edges.</t>
+          <t>Blank for CASP. For RDR, the fee group. The distinct values here DEFINE the set the products sheet must use.</t>
         </is>
       </c>
     </row>
@@ -1999,7 +2005,7 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>tierMin</t>
+          <t>tier</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -2009,12 +2015,12 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Top-account-size lower edge, CURRENCY UNITS. Inclusive.</t>
+          <t>Tier id, e.g. T1. Every row of a tier must carry the same edges.</t>
         </is>
       </c>
     </row>
@@ -2026,12 +2032,12 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>tierMax</t>
+          <t>tierMin</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
@@ -2041,7 +2047,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Upper edge, CURRENCY UNITS, exclusive. BLANK means open-ended.</t>
+          <t>Top-account-size lower edge, CURRENCY UNITS. Inclusive.</t>
         </is>
       </c>
     </row>
@@ -2053,22 +2059,22 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>tierMax</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Management or PMG.</t>
+          <t>Upper edge, CURRENCY UNITS, exclusive. LEAVE IT EMPTY ON THE TOP TIER: an empty cell is how a tier says "and up", and the tier then reads as "$100m and up". Do not write Infinity, inf, or a very large number - all three are refused on load.</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2086,7 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>point</t>
+          <t>source</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
@@ -2095,7 +2101,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Floor, Target or Ceiling. A proposal prices at "&lt;source&gt; &lt;point&gt;", e.g. PMG Floor.</t>
+          <t>Management or PMG.</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2113,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>rate</t>
+          <t>point</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -2117,24 +2123,24 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>number &gt;= 0</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>A PERCENT: 0.45 means 0.45%.</t>
+          <t>Floor, Target or Ceiling. A proposal prices at "&lt;source&gt; &lt;point&gt;", e.g. PMG Floor.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>advisors</t>
+          <t>feeRates</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>rate</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
@@ -2144,12 +2150,12 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number &gt;= 0</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>The advisor name as it should read.</t>
+          <t>A PERCENT: 0.45 means 0.45%.</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2167,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -2176,19 +2182,19 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>The office. The display string is "name - office" with an em dash.</t>
+          <t>The advisor name as it should read.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>assetEstimates</t>
+          <t>advisors</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>Slice</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
@@ -2203,7 +2209,7 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>Currency and hedging, e.g. "USD|Hedged". Sixteen in all.</t>
+          <t>The office. The display string is "name - office" with an em dash.</t>
         </is>
       </c>
     </row>
@@ -2215,7 +2221,7 @@
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>AnalyticsCurrency</t>
+          <t>Slice</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2230,7 +2236,7 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>The currency the figures were actually computed in. Equal to the slice currency unless it was run in another, which the bake manifest then records.</t>
+          <t>Currency and hedging, e.g. "USD|Hedged". Sixteen in all.</t>
         </is>
       </c>
     </row>
@@ -2242,7 +2248,7 @@
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>ReportingName</t>
+          <t>AnalyticsCurrency</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -2257,7 +2263,7 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>One of the 19 asset reporting names on the Valid values sheet.</t>
+          <t>The currency the figures were actually computed in. Equal to the slice currency unless it was run in another, which the bake manifest then records.</t>
         </is>
       </c>
     </row>
@@ -2269,7 +2275,7 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>ReportingName</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -2284,7 +2290,7 @@
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>That asset's category, as on the Valid values sheet.</t>
+          <t>One of the 19 asset reporting names on the Valid values sheet.</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2302,7 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -2306,12 +2312,12 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>FRACTION: 0.006 means 0.6%. Lower bound of the risk-premium estimate.</t>
+          <t>That asset's category, as on the Valid values sheet.</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2329,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Mean</t>
+          <t>Lower</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -2338,7 +2344,7 @@
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>FRACTION. The central risk-premium estimate.</t>
+          <t>FRACTION: 0.006 means 0.6%. Lower bound of the risk-premium estimate.</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2356,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Upper</t>
+          <t>Mean</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -2365,7 +2371,7 @@
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>FRACTION. Upper bound.</t>
+          <t>FRACTION. The central risk-premium estimate.</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2383,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Volatility</t>
+          <t>Upper</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -2392,7 +2398,7 @@
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>FRACTION.</t>
+          <t>FRACTION. Upper bound.</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2410,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Sharpe</t>
+          <t>Volatility</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -2419,7 +2425,7 @@
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>A ratio, not a percent.</t>
+          <t>FRACTION.</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2437,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>TotalReturn</t>
+          <t>Sharpe</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -2446,7 +2452,7 @@
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>FRACTION.</t>
+          <t>A ratio, not a percent.</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2464,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>HedgingRatio</t>
+          <t>TotalReturn</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -2473,7 +2479,7 @@
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>FRACTION: 1.0 means fully hedged.</t>
+          <t>FRACTION.</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2491,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>From</t>
+          <t>HedgingRatio</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -2495,12 +2501,12 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>number</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>ISO date, e.g. 1973-02-28. Start of the estimation window.</t>
+          <t>FRACTION: 1.0 means fully hedged.</t>
         </is>
       </c>
     </row>
@@ -2512,20 +2518,47 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>ISO date, e.g. 1973-02-28. Start of the estimation window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>assetEstimates</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>ISO date. End of the estimation window.</t>
         </is>
@@ -2543,7 +2576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2556,13 +2589,14 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="24" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="14" max="14"/>
+    <col width="24" customWidth="1" min="15" max="15"/>
     <col width="30" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="30" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2603,50 +2637,55 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
+          <t>Share class</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
           <t>Fee schedule</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Fee source</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Fee point</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Fee level (source + point)</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Slice (currency|hedging)</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Asset ticker</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>Asset reporting name</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>Asset ticker</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>Reporting name</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
@@ -2690,50 +2729,55 @@
       </c>
       <c r="H2" s="8" t="inlineStr">
         <is>
+          <t>Dis</t>
+        </is>
+      </c>
+      <c r="I2" s="8" t="inlineStr">
+        <is>
           <t>CASP</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>Management</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>Floor</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr">
+      <c r="L2" s="8" t="inlineStr">
         <is>
           <t>Management Floor</t>
         </is>
       </c>
-      <c r="L2" s="8" t="inlineStr">
+      <c r="M2" s="8" t="inlineStr">
         <is>
           <t>USD|Hedged</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr">
+      <c r="N2" s="8" t="inlineStr">
         <is>
           <t>LHTRYIN</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="O2" s="8" t="inlineStr">
         <is>
           <t>US Dollar Debt</t>
         </is>
       </c>
-      <c r="P2" s="8" t="inlineStr">
+      <c r="Q2" s="8" t="inlineStr">
         <is>
           <t>CSFBMTT</t>
         </is>
       </c>
-      <c r="Q2" s="8" t="inlineStr">
+      <c r="R2" s="8" t="inlineStr">
         <is>
           <t>Tactical Trading</t>
         </is>
       </c>
-      <c r="R2" s="8" t="inlineStr">
+      <c r="S2" s="8" t="inlineStr">
         <is>
           <t>Hedge Funds</t>
         </is>
@@ -2777,50 +2821,55 @@
       </c>
       <c r="H3" s="8" t="inlineStr">
         <is>
+          <t>Acc</t>
+        </is>
+      </c>
+      <c r="I3" s="8" t="inlineStr">
+        <is>
           <t>RDR</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>PMG</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>Management Target</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr">
         <is>
           <t>USD|ISG Hedged</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="N3" s="8" t="inlineStr">
         <is>
           <t>LHYIELD</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="O3" s="8" t="inlineStr">
         <is>
           <t>US High Yield</t>
         </is>
       </c>
-      <c r="P3" s="8" t="inlineStr">
+      <c r="Q3" s="8" t="inlineStr">
         <is>
           <t>CSTEVDH</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="R3" s="8" t="inlineStr">
         <is>
           <t>Event Driven</t>
         </is>
       </c>
-      <c r="R3" s="8" t="inlineStr">
+      <c r="S3" s="8" t="inlineStr">
         <is>
           <t>Hedge Funds</t>
         </is>
@@ -2862,42 +2911,42 @@
           <t>Specialist Active</t>
         </is>
       </c>
-      <c r="J4" s="8" t="inlineStr">
+      <c r="K4" s="8" t="inlineStr">
         <is>
           <t>Ceiling</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Management Ceiling</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>USD|Unhedged</t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr">
         <is>
           <t>FRUS1GR</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="O4" s="8" t="inlineStr">
         <is>
           <t>US Large Cap Growth Equity</t>
         </is>
       </c>
-      <c r="P4" s="8" t="inlineStr">
+      <c r="Q4" s="8" t="inlineStr">
         <is>
           <t>CSTLNSH</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>Equity Long/Short</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Hedge Funds</t>
         </is>
@@ -2939,37 +2988,37 @@
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t>PMG Floor</t>
         </is>
       </c>
-      <c r="L5" s="8" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>USD|Equity Not Hedged</t>
         </is>
       </c>
-      <c r="M5" s="8" t="inlineStr">
+      <c r="N5" s="8" t="inlineStr">
         <is>
           <t>FRUS1VA</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="O5" s="8" t="inlineStr">
         <is>
           <t>US Large Cap Value Equity</t>
         </is>
       </c>
-      <c r="P5" s="8" t="inlineStr">
+      <c r="Q5" s="8" t="inlineStr">
         <is>
           <t>FRUS1GR</t>
         </is>
       </c>
-      <c r="Q5" s="8" t="inlineStr">
+      <c r="R5" s="8" t="inlineStr">
         <is>
           <t>US Large Cap Growth Equity</t>
         </is>
       </c>
-      <c r="R5" s="8" t="inlineStr">
+      <c r="S5" s="8" t="inlineStr">
         <is>
           <t>Public Equity</t>
         </is>
@@ -2991,37 +3040,37 @@
           <t>Asset Allocation</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t>PMG Target</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>GBP|Hedged</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="N6" s="8" t="inlineStr">
         <is>
           <t>FRUSS2L</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="O6" s="8" t="inlineStr">
         <is>
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="P6" s="8" t="inlineStr">
+      <c r="Q6" s="8" t="inlineStr">
         <is>
           <t>FRUS1VA</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="R6" s="8" t="inlineStr">
         <is>
           <t>US Large Cap Value Equity</t>
         </is>
       </c>
-      <c r="R6" s="8" t="inlineStr">
+      <c r="S6" s="8" t="inlineStr">
         <is>
           <t>Public Equity</t>
         </is>
@@ -3038,37 +3087,37 @@
           <t>Private Equity &amp; Other Private Assets</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="L7" s="8" t="inlineStr">
         <is>
           <t>PMG Ceiling</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>GBP|ISG Hedged</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="N7" s="8" t="inlineStr">
         <is>
           <t>MSEXUKL</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>Europe ex-UK Equity</t>
         </is>
       </c>
-      <c r="P7" s="8" t="inlineStr">
+      <c r="Q7" s="8" t="inlineStr">
         <is>
           <t>FRUSS2L</t>
         </is>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
+      <c r="R7" s="8" t="inlineStr">
         <is>
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="R7" s="8" t="inlineStr">
+      <c r="S7" s="8" t="inlineStr">
         <is>
           <t>Public Equity</t>
         </is>
@@ -3085,32 +3134,32 @@
           <t>Asset Allocation Strategies</t>
         </is>
       </c>
-      <c r="L8" s="8" t="inlineStr">
+      <c r="M8" s="8" t="inlineStr">
         <is>
           <t>GBP|Unhedged</t>
         </is>
       </c>
-      <c r="M8" s="8" t="inlineStr">
+      <c r="N8" s="8" t="inlineStr">
         <is>
           <t>MSUTDKL</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="O8" s="8" t="inlineStr">
         <is>
           <t>UK Equity</t>
         </is>
       </c>
-      <c r="P8" s="8" t="inlineStr">
+      <c r="Q8" s="8" t="inlineStr">
         <is>
           <t>LHTRYIN</t>
         </is>
       </c>
-      <c r="Q8" s="8" t="inlineStr">
+      <c r="R8" s="8" t="inlineStr">
         <is>
           <t>US Dollar Debt</t>
         </is>
       </c>
-      <c r="R8" s="8" t="inlineStr">
+      <c r="S8" s="8" t="inlineStr">
         <is>
           <t>Investment Grade Fixed Income</t>
         </is>
@@ -3122,369 +3171,369 @@
           <t>All Equity</t>
         </is>
       </c>
-      <c r="L9" s="8" t="inlineStr">
+      <c r="M9" s="8" t="inlineStr">
         <is>
           <t>GBP|Equity Not Hedged</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="N9" s="8" t="inlineStr">
         <is>
           <t>MSJPANL</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="O9" s="8" t="inlineStr">
         <is>
           <t>Japanese Equity</t>
         </is>
       </c>
-      <c r="P9" s="8" t="inlineStr">
+      <c r="Q9" s="8" t="inlineStr">
         <is>
           <t>LHUT1T3</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="R9" s="8" t="inlineStr">
         <is>
           <t>Tactical Tilt Fund</t>
         </is>
       </c>
-      <c r="R9" s="8" t="inlineStr">
+      <c r="S9" s="8" t="inlineStr">
         <is>
           <t>Asset Allocation Strategies</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="L10" s="8" t="inlineStr">
+      <c r="M10" s="8" t="inlineStr">
         <is>
           <t>CHF|Hedged</t>
         </is>
       </c>
-      <c r="M10" s="8" t="inlineStr">
+      <c r="N10" s="8" t="inlineStr">
         <is>
           <t>MSPXJPL</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr">
+      <c r="O10" s="8" t="inlineStr">
         <is>
           <t>Asia-Pacific Equity</t>
         </is>
       </c>
-      <c r="P10" s="8" t="inlineStr">
+      <c r="Q10" s="8" t="inlineStr">
         <is>
           <t>LHYIELD</t>
         </is>
       </c>
-      <c r="Q10" s="8" t="inlineStr">
+      <c r="R10" s="8" t="inlineStr">
         <is>
           <t>US High Yield</t>
         </is>
       </c>
-      <c r="R10" s="8" t="inlineStr">
+      <c r="S10" s="8" t="inlineStr">
         <is>
           <t>Other Fixed Income</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="L11" s="8" t="inlineStr">
+      <c r="M11" s="8" t="inlineStr">
         <is>
           <t>CHF|ISG Hedged</t>
         </is>
       </c>
-      <c r="M11" s="8" t="inlineStr">
+      <c r="N11" s="8" t="inlineStr">
         <is>
           <t>MSEMKF$</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="O11" s="8" t="inlineStr">
         <is>
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="P11" s="8" t="inlineStr">
+      <c r="Q11" s="8" t="inlineStr">
         <is>
           <t>MSEMKF$</t>
         </is>
       </c>
-      <c r="Q11" s="8" t="inlineStr">
+      <c r="R11" s="8" t="inlineStr">
         <is>
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="R11" s="8" t="inlineStr">
+      <c r="S11" s="8" t="inlineStr">
         <is>
           <t>Public Equity</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="L12" s="8" t="inlineStr">
+      <c r="M12" s="8" t="inlineStr">
         <is>
           <t>CHF|Unhedged</t>
         </is>
       </c>
-      <c r="M12" s="8" t="inlineStr">
+      <c r="N12" s="8" t="inlineStr">
         <is>
           <t>CSTEVDH</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr">
+      <c r="O12" s="8" t="inlineStr">
         <is>
           <t>Event Driven</t>
         </is>
       </c>
-      <c r="P12" s="8" t="inlineStr">
+      <c r="Q12" s="8" t="inlineStr">
         <is>
           <t>MSEXUKL</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="R12" s="8" t="inlineStr">
         <is>
           <t>Europe ex-UK Equity</t>
         </is>
       </c>
-      <c r="R12" s="8" t="inlineStr">
+      <c r="S12" s="8" t="inlineStr">
         <is>
           <t>Public Equity</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="L13" s="8" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>CHF|Equity Not Hedged</t>
         </is>
       </c>
-      <c r="M13" s="8" t="inlineStr">
+      <c r="N13" s="8" t="inlineStr">
         <is>
           <t>CSTLNSH</t>
         </is>
       </c>
-      <c r="N13" s="8" t="inlineStr">
+      <c r="O13" s="8" t="inlineStr">
         <is>
           <t>Equity Long/Short</t>
         </is>
       </c>
-      <c r="P13" s="8" t="inlineStr">
+      <c r="Q13" s="8" t="inlineStr">
         <is>
           <t>MSJPANL</t>
         </is>
       </c>
-      <c r="Q13" s="8" t="inlineStr">
+      <c r="R13" s="8" t="inlineStr">
         <is>
           <t>Japanese Equity</t>
         </is>
       </c>
-      <c r="R13" s="8" t="inlineStr">
+      <c r="S13" s="8" t="inlineStr">
         <is>
           <t>Public Equity</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="L14" s="8" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>EUR|Hedged</t>
         </is>
       </c>
-      <c r="M14" s="8" t="inlineStr">
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t>CSFBMTT</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>Tactical Trading</t>
         </is>
       </c>
-      <c r="P14" s="8" t="inlineStr">
+      <c r="Q14" s="8" t="inlineStr">
         <is>
           <t>MSPXJPL</t>
         </is>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="R14" s="8" t="inlineStr">
         <is>
           <t>Asia-Pacific Equity</t>
         </is>
       </c>
-      <c r="R14" s="8" t="inlineStr">
+      <c r="S14" s="8" t="inlineStr">
         <is>
           <t>Public Equity</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="L15" s="8" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t>EUR|ISG Hedged</t>
         </is>
       </c>
-      <c r="M15" s="8" t="inlineStr">
+      <c r="N15" s="8" t="inlineStr">
         <is>
           <t>PE_BUYOUT</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr">
+      <c r="O15" s="8" t="inlineStr">
         <is>
           <t>Buyout</t>
         </is>
       </c>
-      <c r="P15" s="8" t="inlineStr">
+      <c r="Q15" s="8" t="inlineStr">
         <is>
           <t>MSUTDKL</t>
         </is>
       </c>
-      <c r="Q15" s="8" t="inlineStr">
+      <c r="R15" s="8" t="inlineStr">
         <is>
           <t>UK Equity</t>
         </is>
       </c>
-      <c r="R15" s="8" t="inlineStr">
+      <c r="S15" s="8" t="inlineStr">
         <is>
           <t>Public Equity</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="L16" s="8" t="inlineStr">
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>EUR|Unhedged</t>
         </is>
       </c>
-      <c r="M16" s="8" t="inlineStr">
+      <c r="N16" s="8" t="inlineStr">
         <is>
           <t>PE_GROWTH</t>
         </is>
       </c>
-      <c r="N16" s="8" t="inlineStr">
+      <c r="O16" s="8" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="P16" s="8" t="inlineStr">
+      <c r="Q16" s="8" t="inlineStr">
         <is>
           <t>PA_REAL_ESTATE</t>
         </is>
       </c>
-      <c r="Q16" s="8" t="inlineStr">
+      <c r="R16" s="8" t="inlineStr">
         <is>
           <t>Core Real Estate</t>
         </is>
       </c>
-      <c r="R16" s="8" t="inlineStr">
+      <c r="S16" s="8" t="inlineStr">
         <is>
           <t>Other Private Assets</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="L17" s="8" t="inlineStr">
+      <c r="M17" s="8" t="inlineStr">
         <is>
           <t>EUR|Equity Not Hedged</t>
         </is>
       </c>
-      <c r="M17" s="8" t="inlineStr">
+      <c r="N17" s="8" t="inlineStr">
         <is>
           <t>PE_VENTURE</t>
         </is>
       </c>
-      <c r="N17" s="8" t="inlineStr">
+      <c r="O17" s="8" t="inlineStr">
         <is>
           <t>Venture</t>
         </is>
       </c>
-      <c r="P17" s="8" t="inlineStr">
+      <c r="Q17" s="8" t="inlineStr">
         <is>
           <t>PE_BUYOUT</t>
         </is>
       </c>
-      <c r="Q17" s="8" t="inlineStr">
+      <c r="R17" s="8" t="inlineStr">
         <is>
           <t>Buyout</t>
         </is>
       </c>
-      <c r="R17" s="8" t="inlineStr">
+      <c r="S17" s="8" t="inlineStr">
         <is>
           <t>Private Equity</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="M18" s="8" t="inlineStr">
+      <c r="N18" s="8" t="inlineStr">
         <is>
           <t>PRIVATE_CREDIT</t>
         </is>
       </c>
-      <c r="N18" s="8" t="inlineStr">
+      <c r="O18" s="8" t="inlineStr">
         <is>
           <t>Private Credit</t>
         </is>
       </c>
-      <c r="P18" s="8" t="inlineStr">
+      <c r="Q18" s="8" t="inlineStr">
         <is>
           <t>PE_GROWTH</t>
         </is>
       </c>
-      <c r="Q18" s="8" t="inlineStr">
+      <c r="R18" s="8" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="R18" s="8" t="inlineStr">
+      <c r="S18" s="8" t="inlineStr">
         <is>
           <t>Private Equity</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="M19" s="8" t="inlineStr">
+      <c r="N19" s="8" t="inlineStr">
         <is>
           <t>PA_REAL_ESTATE</t>
         </is>
       </c>
-      <c r="N19" s="8" t="inlineStr">
+      <c r="O19" s="8" t="inlineStr">
         <is>
           <t>Core Real Estate</t>
         </is>
       </c>
-      <c r="P19" s="8" t="inlineStr">
+      <c r="Q19" s="8" t="inlineStr">
         <is>
           <t>PE_VENTURE</t>
         </is>
       </c>
-      <c r="Q19" s="8" t="inlineStr">
+      <c r="R19" s="8" t="inlineStr">
         <is>
           <t>Venture</t>
         </is>
       </c>
-      <c r="R19" s="8" t="inlineStr">
+      <c r="S19" s="8" t="inlineStr">
         <is>
           <t>Private Equity</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="M20" s="8" t="inlineStr">
+      <c r="N20" s="8" t="inlineStr">
         <is>
           <t>LHUT1T3</t>
         </is>
       </c>
-      <c r="N20" s="8" t="inlineStr">
+      <c r="O20" s="8" t="inlineStr">
         <is>
           <t>Tactical Tilt Fund</t>
         </is>
       </c>
-      <c r="P20" s="8" t="inlineStr">
+      <c r="Q20" s="8" t="inlineStr">
         <is>
           <t>PRIVATE_CREDIT</t>
         </is>
       </c>
-      <c r="Q20" s="8" t="inlineStr">
+      <c r="R20" s="8" t="inlineStr">
         <is>
           <t>Private Credit</t>
         </is>
       </c>
-      <c r="R20" s="8" t="inlineStr">
+      <c r="S20" s="8" t="inlineStr">
         <is>
           <t>Other Private Assets</t>
         </is>
@@ -3560,7 +3609,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2:B5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
-      <formula1>'Valid values'!$M$2:$M$20</formula1>
+      <formula1>'Valid values'!$N$2:$N$20</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3575,7 +3624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:N3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -3584,13 +3633,14 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="22" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="17" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
     <col width="23" customWidth="1" min="13" max="13"/>
+    <col width="23" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3626,35 +3676,40 @@
       </c>
       <c r="G1" s="4" t="inlineStr">
         <is>
+          <t>ShareClass</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Liquidity</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>ExposureCurrency</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>ProductCost</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>FeeGroup</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>DistributionYield</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>MinimumInvestment</t>
         </is>
@@ -3689,31 +3744,36 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
+          <t>Dis</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
           <t>Internal</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="K2" s="3" t="n">
         <v>0.25</v>
       </c>
-      <c r="K2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="M2" s="3" t="n">
         <v>3.2</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="N2" s="3" t="n">
         <v>5000000</v>
       </c>
     </row>
@@ -3746,38 +3806,46 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
+          <t>Dis</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
           <t>Internal</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="K3" s="3" t="n">
         <v>0.28</v>
       </c>
-      <c r="K3" s="3" t="inlineStr">
+      <c r="L3" s="3" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="M3" s="3" t="n">
         <v>4.8</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="N3" s="3" t="n">
         <v>5000000</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="K2:K5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
+  <dataValidations count="2">
+    <dataValidation sqref="L2:L5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
       <formula1>'Valid values'!$G$2:$G$6</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
+      <formula1>'Valid values'!$H$2:$H$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3996,15 +4064,13 @@
       <c r="B3" s="3" t="n"/>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>10000000</v>
-      </c>
+        <v>100000000</v>
+      </c>
+      <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Management</t>
@@ -4012,26 +4078,26 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Floor</t>
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>0.6</v>
+        <v>0.17</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="A2:A5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
-      <formula1>'Valid values'!$H$2:$H$3</formula1>
+      <formula1>'Valid values'!$I$2:$I$3</formula1>
     </dataValidation>
     <dataValidation sqref="B2:B5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
       <formula1>'Valid values'!$G$2:$G$6</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
-      <formula1>'Valid values'!$I$2:$I$3</formula1>
+      <formula1>'Valid values'!$J$2:$J$3</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
-      <formula1>'Valid values'!$J$2:$J$4</formula1>
+      <formula1>'Valid values'!$K$2:$K$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4296,10 +4362,10 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="A2:A5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
-      <formula1>'Valid values'!$L$2:$L$17</formula1>
+      <formula1>'Valid values'!$M$2:$M$17</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
-      <formula1>'Valid values'!$N$2:$N$20</formula1>
+      <formula1>'Valid values'!$O$2:$O$20</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/epsilon-phi-core/proposal-tool/dataTemplates/ProposalTool_DataTemplates.xlsx
+++ b/epsilon-phi-core/proposal-tool/dataTemplates/ProposalTool_DataTemplates.xlsx
@@ -13,10 +13,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="saaPortfolios" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="products" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sleeves" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="feeRates" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="advisors" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assetEstimates" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="portfolioAnalytics" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sleeveRules" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="feeRates" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="advisors" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assetEstimates" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="portfolioAnalytics" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -359,19 +360,25 @@
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>Sleeve (yes, text (&lt;= 80))
-The sleeve name. Unique within a variant and category.</t>
+The sleeve name: what a PWA picks. Its editions share it. Unique within a variant and category together with the Edition.</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Edition (no, text (&lt;= 80))
+BLANK for the fallback edition, which applies wherever no other edition of the name does; or the desk's short label for an edition that is only for particular strategic portfolios ("GBP", "GBP ex-Alts"). A labelled edition must have rules on the sleeveRules sheet; a fallback must not. At most one fallback per name. The header without this column is still accepted: every row is then a fallback.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <t>ProductId (yes, text)
 Must exist in the products sheet.</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="F1" authorId="0" shapeId="0">
       <text>
         <t>Weight (yes, number)
-A FRACTION. One sleeve's rows must sum to 1 within 0.000001.</t>
+A FRACTION. One edition's rows must sum to 1 within 0.000001.</t>
       </text>
     </comment>
   </commentList>
@@ -386,50 +393,44 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>schedule (yes, text)
-CASP (one rate for all) or RDR (a rate per fee group).</t>
+        <t>Variant (yes, text)
+As on the sleeves sheet.</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>feeGroup (yes for RDR, text)
-Blank for CASP. For RDR, the fee group. The distinct values here DEFINE the set the products sheet must use.</t>
+        <t>Category (yes, text)
+As on the sleeves sheet.</t>
       </text>
     </comment>
     <comment ref="C1" authorId="0" shapeId="0">
       <text>
-        <t>tier (yes, text)
-Tier id, e.g. T1. Every row of a tier must carry the same edges.</t>
+        <t>Sleeve (yes, text)
+The sleeve name, exactly as on the sleeves sheet.</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>tierMin (yes, number)
-Top-account-size lower edge, CURRENCY UNITS. Inclusive.</t>
+        <t>Edition (yes, text)
+The edition label, exactly as on the sleeves sheet. Never blank here: the fallback has no rules.</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>tierMax (no, number)
-Upper edge, CURRENCY UNITS, exclusive. LEAVE IT EMPTY ON THE TOP TIER: an empty cell is how a tier says "and up", and the tier then reads as "$100m and up". Do not write Infinity, inf, or a very large number - all three are refused on load.</t>
+        <t>Currency (no, text)
+One or more currencies from the Valid values sheet, several separated by | ("GBP" or "GBP|EUR"). Blank means any currency.</t>
       </text>
     </comment>
     <comment ref="F1" authorId="0" shapeId="0">
       <text>
-        <t>source (yes, text)
-Management or PMG.</t>
+        <t>RiskLevel (no, text)
+One or more risk levels from the Valid values sheet, several separated by | ("Moderate" or "Moderate|ModAgg"). Blank means any risk level.</t>
       </text>
     </comment>
     <comment ref="G1" authorId="0" shapeId="0">
       <text>
-        <t>point (yes, text)
-Floor, Target or Ceiling. A proposal prices at "&lt;source&gt; &lt;point&gt;", e.g. PMG Floor.</t>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
-      <text>
-        <t>rate (yes, number &gt;= 0)
-A PERCENT: 0.45 means 0.45%.</t>
+        <t>AllocationType (no, text)
+One or more allocation types from the Valid values sheet, several separated by |, and NA for the all-equity book ("ex-Alts" or "Full|Core|ex-HFs|NA"). Blank means any. At least one of the three cells must be filled: a rule that constrains nothing is refused. Hedging and the real-assets exclusion are not rule fields.</t>
       </text>
     </comment>
   </commentList>
@@ -444,14 +445,50 @@
   <commentList>
     <comment ref="A1" authorId="0" shapeId="0">
       <text>
-        <t>name (yes, text)
-The advisor name as it should read.</t>
+        <t>schedule (yes, text)
+CASP (one rate for all) or RDR (a rate per fee group).</t>
       </text>
     </comment>
     <comment ref="B1" authorId="0" shapeId="0">
       <text>
-        <t>office (yes, text)
-The office. The display string is "name - office" with an em dash.</t>
+        <t>feeGroup (yes for RDR, text)
+Blank for CASP. For RDR, the fee group. The distinct values here DEFINE the set the products sheet must use.</t>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0" shapeId="0">
+      <text>
+        <t>tier (yes, text)
+Tier id, e.g. T1. Every row of a tier must carry the same edges.</t>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>tierMin (yes, number)
+Top-account-size lower edge, CURRENCY UNITS. Inclusive.</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>tierMax (no, number)
+Upper edge, CURRENCY UNITS, exclusive. LEAVE IT EMPTY ON THE TOP TIER: an empty cell is how a tier says "and up", and the tier then reads as "$100m and up". Do not write Infinity, inf, or a very large number - all three are refused on load.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>source (yes, text)
+Management or PMG.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>point (yes, text)
+Floor, Target or Ceiling. A proposal prices at "&lt;source&gt; &lt;point&gt;", e.g. PMG Floor.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>rate (yes, number &gt;= 0)
+A PERCENT: 0.45 means 0.45%.</t>
       </text>
     </comment>
   </commentList>
@@ -459,6 +496,28 @@
 </file>
 
 <file path=xl/comments/comment6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Proposal Tool</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0">
+      <text>
+        <t>name (yes, text)
+The advisor name as it should read.</t>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>office (yes, text)
+The office. The display string is "name - office" with an em dash.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments/comment7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>Proposal Tool</author>
@@ -836,7 +895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -999,17 +1058,17 @@
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>feeRates</t>
+          <t>sleeveRules</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>feeRates.csv</t>
+          <t>sleeveRules.csv</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>SCENARIO_FEES_SOURCE</t>
+          <t>SCENARIO_SLEEVES_RULES</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1024,129 +1083,161 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>The rate card: one row per cell. Deliver it through "feeTools --diff &lt;csv&gt;" then "--accept", which records the version and clears the placeholder flag the rail, the workbook and the bake manifest all read.</t>
+          <t>Which strategic portfolios each labelled edition on the sleeves sheet is for: one row per rule. An edition with several rows applies where ANY of them matches. A rule matches a portfolio when every filled cell contains the portfolio's value; a blank cell means any. Read with the sleeves sheet, once, on the first start; optional - a library with no editions needs no rules. Two editions of one name may not both claim a portfolio: the load refuses and names the clash.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>advisors</t>
+          <t>feeRates</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>advisors.xlsx (inside the package, beside advisors.py)</t>
+          <t>feeRates.csv</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>none - there is no override</t>
+          <t>SCENARIO_FEES_SOURCE</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>XLSX, first sheet</t>
+          <t>CSV</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>replace the packaged file</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>The Primary PWA directory behind the typeahead. A mandate's Primary PWA must equal a display string exactly, or creating a scenario is refused.</t>
+          <t>The rate card: one row per cell. Deliver it through "feeTools --diff &lt;csv&gt;" then "--accept", which records the version and clears the placeholder flag the rail, the workbook and the bake manifest all read.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>assetEstimates</t>
+          <t>advisors</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>assetEstimates.json</t>
+          <t>advisors.xlsx (inside the package, beside advisors.py)</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>SCENARIO_ASSET_ESTIMATES</t>
+          <t>none - there is no override</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>JSON (see note)</t>
+          <t>XLSX, first sheet</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>replace the packaged file</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>The per-asset long-term estimates behind the workbook's assumptions sheet, one block per currency-and-hedging slice. THE SERVICE READS JSON: fill this table in, then convert it - the shape is on the portfolioAnalytics sheet.</t>
+          <t>The Primary PWA directory behind the typeahead. A mandate's Primary PWA must equal a display string exactly, or creating a scenario is refused.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>assetEstimates</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>assetEstimates.json</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>SCENARIO_ASSET_ESTIMATES</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>JSON (see note)</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>The per-asset long-term estimates behind the workbook's assumptions sheet, one block per currency-and-hedging slice. THE SERVICE READS JSON: fill this table in, then convert it - the shape is on the portfolioAnalytics sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
           <t>portfolioAnalytics</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>&lt;slice&gt;.json + manifest.json</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>SCENARIO_BAKED_DIR</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>JSON</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>The risk and return figures themselves. Generated, not typed - see that sheet.</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>Check your files with:</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>python -m cyrus_pmg.pmgService.scenario.bake --census        # the SAA extract: 0 unparsed, no unknown tickers</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>python -m cyrus_pmg.pmgService.scenario.sleeveTools --census # the sleeve library: no broken sleeves, no orphans</t>
+          <t>python -m cyrus_pmg.pmgService.scenario.bake --census        # the SAA extract: 0 unparsed, no unknown tickers</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>python -m cyrus_pmg.pmgService.scenario.sleeveTools --census # the sleeve library: no broken sleeves, no orphans</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
         <is>
           <t>python -m cyrus_pmg.pmgService.scenario.feeTools --census    # the rate card, and whether it is still a placeholder</t>
         </is>
@@ -1162,6 +1253,218 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="008A6D1B"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Slice</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>AnalyticsCurrency</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>ReportingName</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Lower</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Upper</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Volatility</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>TotalReturn</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>HedgingRatio</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>To</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>USD|Hedged</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>US Dollar Debt</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>Investment Grade Fixed Income</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>0.005996386355446893</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>0.01114331525420141</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>0.01629024415295593</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>0.03218769340281281</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.3461980053913284</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>0.03614331525420142</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>1973-02-28</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>USD|Hedged</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>US High Yield</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Other Fixed Income</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>0.0169879773721</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.03012601151314502</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>0.04326404565419004</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>0.0821622025806448</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0.3666650913304739</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.05512601151314502</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>1983-08-31</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
+      <formula1>'Valid values'!$N$2:$N$17</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
+      <formula1>'Valid values'!$P$2:$P$20</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="0012233F"/>
@@ -1305,7 +1608,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1885,7 +2188,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>The sleeve name. Unique within a variant and category.</t>
+          <t>The sleeve name: what a PWA picks. Its editions share it. Unique within a variant and category together with the Edition.</t>
         </is>
       </c>
     </row>
@@ -1897,22 +2200,22 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>ProductId</t>
+          <t>Edition</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>text (&lt;= 80)</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>Must exist in the products sheet.</t>
+          <t>BLANK for the fallback edition, which applies wherever no other edition of the name does; or the desk's short label for an edition that is only for particular strategic portfolios ("GBP", "GBP ex-Alts"). A labelled edition must have rules on the sleeveRules sheet; a fallback must not. At most one fallback per name. The header without this column is still accepted: every row is then a fallback.</t>
         </is>
       </c>
     </row>
@@ -1924,7 +2227,7 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>Weight</t>
+          <t>ProductId</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
@@ -1934,24 +2237,24 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>A FRACTION. One sleeve's rows must sum to 1 within 0.000001.</t>
+          <t>Must exist in the products sheet.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>feeRates</t>
+          <t>sleeves</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>schedule</t>
+          <t>Weight</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
@@ -1961,29 +2264,29 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>CASP (one rate for all) or RDR (a rate per fee group).</t>
+          <t>A FRACTION. One edition's rows must sum to 1 within 0.000001.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>feeRates</t>
+          <t>sleeveRules</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>feeGroup</t>
+          <t>Variant</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>yes for RDR</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
@@ -1993,19 +2296,19 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Blank for CASP. For RDR, the fee group. The distinct values here DEFINE the set the products sheet must use.</t>
+          <t>As on the sleeves sheet.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>feeRates</t>
+          <t>sleeveRules</t>
         </is>
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>tier</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
@@ -2020,19 +2323,19 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>Tier id, e.g. T1. Every row of a tier must carry the same edges.</t>
+          <t>As on the sleeves sheet.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
         <is>
-          <t>feeRates</t>
+          <t>sleeveRules</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>tierMin</t>
+          <t>Sleeve</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
@@ -2042,56 +2345,56 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>Top-account-size lower edge, CURRENCY UNITS. Inclusive.</t>
+          <t>The sleeve name, exactly as on the sleeves sheet.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>feeRates</t>
+          <t>sleeveRules</t>
         </is>
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>tierMax</t>
+          <t>Edition</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>Upper edge, CURRENCY UNITS, exclusive. LEAVE IT EMPTY ON THE TOP TIER: an empty cell is how a tier says "and up", and the tier then reads as "$100m and up". Do not write Infinity, inf, or a very large number - all three are refused on load.</t>
+          <t>The edition label, exactly as on the sleeves sheet. Never blank here: the fallback has no rules.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
         <is>
-          <t>feeRates</t>
+          <t>sleeveRules</t>
         </is>
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
@@ -2101,24 +2404,24 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>Management or PMG.</t>
+          <t>One or more currencies from the Valid values sheet, several separated by | ("GBP" or "GBP|EUR"). Blank means any currency.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>feeRates</t>
+          <t>sleeveRules</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>point</t>
+          <t>RiskLevel</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
@@ -2128,46 +2431,46 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Floor, Target or Ceiling. A proposal prices at "&lt;source&gt; &lt;point&gt;", e.g. PMG Floor.</t>
+          <t>One or more risk levels from the Valid values sheet, several separated by | ("Moderate" or "Moderate|ModAgg"). Blank means any risk level.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
         <is>
-          <t>feeRates</t>
+          <t>sleeveRules</t>
         </is>
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>rate</t>
+          <t>AllocationType</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>number &gt;= 0</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>A PERCENT: 0.45 means 0.45%.</t>
+          <t>One or more allocation types from the Valid values sheet, several separated by |, and NA for the all-equity book ("ex-Alts" or "Full|Core|ex-HFs|NA"). Blank means any. At least one of the three cells must be filled: a rule that constrains nothing is refused. Hedging and the real-assets exclusion are not rule fields.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>advisors</t>
+          <t>feeRates</t>
         </is>
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>schedule</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -2182,24 +2485,24 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>The advisor name as it should read.</t>
+          <t>CASP (one rate for all) or RDR (a rate per fee group).</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>advisors</t>
+          <t>feeRates</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>office</t>
+          <t>feeGroup</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>yes for RDR</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
@@ -2209,19 +2512,19 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>The office. The display string is "name - office" with an em dash.</t>
+          <t>Blank for CASP. For RDR, the fee group. The distinct values here DEFINE the set the products sheet must use.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>assetEstimates</t>
+          <t>feeRates</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Slice</t>
+          <t>tier</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -2236,19 +2539,19 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>Currency and hedging, e.g. "USD|Hedged". Sixteen in all.</t>
+          <t>Tier id, e.g. T1. Every row of a tier must carry the same edges.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>assetEstimates</t>
+          <t>feeRates</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>AnalyticsCurrency</t>
+          <t>tierMin</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -2258,51 +2561,51 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>The currency the figures were actually computed in. Equal to the slice currency unless it was run in another, which the bake manifest then records.</t>
+          <t>Top-account-size lower edge, CURRENCY UNITS. Inclusive.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>assetEstimates</t>
+          <t>feeRates</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>ReportingName</t>
+          <t>tierMax</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>number</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>One of the 19 asset reporting names on the Valid values sheet.</t>
+          <t>Upper edge, CURRENCY UNITS, exclusive. LEAVE IT EMPTY ON THE TOP TIER: an empty cell is how a tier says "and up", and the tier then reads as "$100m and up". Do not write Infinity, inf, or a very large number - all three are refused on load.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>assetEstimates</t>
+          <t>feeRates</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>Category</t>
+          <t>source</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
@@ -2317,19 +2620,19 @@
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>That asset's category, as on the Valid values sheet.</t>
+          <t>Management or PMG.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>assetEstimates</t>
+          <t>feeRates</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>Lower</t>
+          <t>point</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -2339,24 +2642,24 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>FRACTION: 0.006 means 0.6%. Lower bound of the risk-premium estimate.</t>
+          <t>Floor, Target or Ceiling. A proposal prices at "&lt;source&gt; &lt;point&gt;", e.g. PMG Floor.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>assetEstimates</t>
+          <t>feeRates</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Mean</t>
+          <t>rate</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -2366,24 +2669,24 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>number &gt;= 0</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>FRACTION. The central risk-premium estimate.</t>
+          <t>A PERCENT: 0.45 means 0.45%.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>assetEstimates</t>
+          <t>advisors</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Upper</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -2393,24 +2696,24 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
         <is>
-          <t>FRACTION. Upper bound.</t>
+          <t>The advisor name as it should read.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>assetEstimates</t>
+          <t>advisors</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Volatility</t>
+          <t>office</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -2420,12 +2723,12 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>FRACTION.</t>
+          <t>The office. The display string is "name - office" with an em dash.</t>
         </is>
       </c>
     </row>
@@ -2437,7 +2740,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>Sharpe</t>
+          <t>Slice</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -2447,12 +2750,12 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
         <is>
-          <t>A ratio, not a percent.</t>
+          <t>Currency and hedging, e.g. "USD|Hedged". Sixteen in all.</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2767,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>TotalReturn</t>
+          <t>AnalyticsCurrency</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -2474,12 +2777,12 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>FRACTION.</t>
+          <t>The currency the figures were actually computed in. Equal to the slice currency unless it was run in another, which the bake manifest then records.</t>
         </is>
       </c>
     </row>
@@ -2491,7 +2794,7 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>HedgingRatio</t>
+          <t>ReportingName</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
@@ -2501,12 +2804,12 @@
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>number</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>FRACTION: 1.0 means fully hedged.</t>
+          <t>One of the 19 asset reporting names on the Valid values sheet.</t>
         </is>
       </c>
     </row>
@@ -2518,7 +2821,7 @@
       </c>
       <c r="B47" s="5" t="inlineStr">
         <is>
-          <t>From</t>
+          <t>Category</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
@@ -2528,12 +2831,12 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>ISO date, e.g. 1973-02-28. Start of the estimation window.</t>
+          <t>That asset's category, as on the Valid values sheet.</t>
         </is>
       </c>
     </row>
@@ -2545,20 +2848,236 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
+          <t>Lower</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>FRACTION: 0.006 means 0.6%. Lower bound of the risk-premium estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>assetEstimates</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>Mean</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>FRACTION. The central risk-premium estimate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>assetEstimates</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Upper</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>FRACTION. Upper bound.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>assetEstimates</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Volatility</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>FRACTION.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>assetEstimates</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>Sharpe</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>A ratio, not a percent.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>assetEstimates</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>TotalReturn</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>FRACTION.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>assetEstimates</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>HedgingRatio</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>number</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>FRACTION: 1.0 means fully hedged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>assetEstimates</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>From</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>ISO date, e.g. 1973-02-28. Start of the estimation window.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>assetEstimates</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
           <t>To</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="D48" s="5" t="inlineStr">
+      <c r="D56" s="5" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>ISO date. End of the estimation window.</t>
         </is>
@@ -2576,27 +3095,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="19" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-    <col width="25" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="24" customWidth="1" min="15" max="15"/>
-    <col width="30" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="25" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="24" customWidth="1" min="16" max="16"/>
     <col width="30" customWidth="1" min="18" max="18"/>
     <col width="30" customWidth="1" min="19" max="19"/>
+    <col width="30" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2622,70 +3142,75 @@
       </c>
       <c r="E1" s="4" t="inlineStr">
         <is>
+          <t>Allocation type in a rule (NA = all-equity)</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
           <t>Implementation type</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Sleeve category</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Fee group</t>
         </is>
       </c>
-      <c r="H1" s="4" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Share class</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Fee schedule</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Fee source</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Fee point</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Fee level (source + point)</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>Slice (currency|hedging)</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>Asset ticker</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>Asset reporting name</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>Asset ticker</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>Reporting name</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
@@ -2714,70 +3239,75 @@
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
+          <t>Full</t>
+        </is>
+      </c>
+      <c r="F2" s="8" t="inlineStr">
+        <is>
           <t>PMG Multi-Asset Portfolio</t>
         </is>
       </c>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr">
         <is>
           <t>Investment Grade Fixed Income</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="H2" s="8" t="inlineStr">
         <is>
           <t>Passive</t>
         </is>
       </c>
-      <c r="H2" s="8" t="inlineStr">
+      <c r="I2" s="8" t="inlineStr">
         <is>
           <t>Dis</t>
         </is>
       </c>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="J2" s="8" t="inlineStr">
         <is>
           <t>CASP</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>Management</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr">
+      <c r="L2" s="8" t="inlineStr">
         <is>
           <t>Floor</t>
         </is>
       </c>
-      <c r="L2" s="8" t="inlineStr">
+      <c r="M2" s="8" t="inlineStr">
         <is>
           <t>Management Floor</t>
         </is>
       </c>
-      <c r="M2" s="8" t="inlineStr">
+      <c r="N2" s="8" t="inlineStr">
         <is>
           <t>USD|Hedged</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="O2" s="8" t="inlineStr">
         <is>
           <t>LHTRYIN</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="P2" s="8" t="inlineStr">
         <is>
           <t>US Dollar Debt</t>
         </is>
       </c>
-      <c r="Q2" s="8" t="inlineStr">
+      <c r="R2" s="8" t="inlineStr">
         <is>
           <t>CSFBMTT</t>
         </is>
       </c>
-      <c r="R2" s="8" t="inlineStr">
+      <c r="S2" s="8" t="inlineStr">
         <is>
           <t>Tactical Trading</t>
         </is>
       </c>
-      <c r="S2" s="8" t="inlineStr">
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>Hedge Funds</t>
         </is>
@@ -2806,70 +3336,75 @@
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
           <t>PMG ESG</t>
         </is>
       </c>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>Hybrid Fixed Income</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
         <is>
           <t>Core Active</t>
         </is>
       </c>
-      <c r="H3" s="8" t="inlineStr">
+      <c r="I3" s="8" t="inlineStr">
         <is>
           <t>Acc</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>RDR</t>
         </is>
       </c>
-      <c r="J3" s="8" t="inlineStr">
+      <c r="K3" s="8" t="inlineStr">
         <is>
           <t>PMG</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr">
         <is>
           <t>Management Target</t>
         </is>
       </c>
-      <c r="M3" s="8" t="inlineStr">
+      <c r="N3" s="8" t="inlineStr">
         <is>
           <t>USD|ISG Hedged</t>
         </is>
       </c>
-      <c r="N3" s="8" t="inlineStr">
+      <c r="O3" s="8" t="inlineStr">
         <is>
           <t>LHYIELD</t>
         </is>
       </c>
-      <c r="O3" s="8" t="inlineStr">
+      <c r="P3" s="8" t="inlineStr">
         <is>
           <t>US High Yield</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="R3" s="8" t="inlineStr">
         <is>
           <t>CSTEVDH</t>
         </is>
       </c>
-      <c r="R3" s="8" t="inlineStr">
+      <c r="S3" s="8" t="inlineStr">
         <is>
           <t>Event Driven</t>
         </is>
       </c>
-      <c r="S3" s="8" t="inlineStr">
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>Hedge Funds</t>
         </is>
@@ -2898,55 +3433,60 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
+          <t>ex-Alts</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
           <t>US Onshore</t>
         </is>
       </c>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="G4" s="8" t="inlineStr">
         <is>
           <t>Other Fixed Income</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="H4" s="8" t="inlineStr">
         <is>
           <t>Specialist Active</t>
         </is>
       </c>
-      <c r="K4" s="8" t="inlineStr">
+      <c r="L4" s="8" t="inlineStr">
         <is>
           <t>Ceiling</t>
         </is>
       </c>
-      <c r="L4" s="8" t="inlineStr">
+      <c r="M4" s="8" t="inlineStr">
         <is>
           <t>Management Ceiling</t>
         </is>
       </c>
-      <c r="M4" s="8" t="inlineStr">
+      <c r="N4" s="8" t="inlineStr">
         <is>
           <t>USD|Unhedged</t>
         </is>
       </c>
-      <c r="N4" s="8" t="inlineStr">
+      <c r="O4" s="8" t="inlineStr">
         <is>
           <t>FRUS1GR</t>
         </is>
       </c>
-      <c r="O4" s="8" t="inlineStr">
+      <c r="P4" s="8" t="inlineStr">
         <is>
           <t>US Large Cap Growth Equity</t>
         </is>
       </c>
-      <c r="Q4" s="8" t="inlineStr">
+      <c r="R4" s="8" t="inlineStr">
         <is>
           <t>CSTLNSH</t>
         </is>
       </c>
-      <c r="R4" s="8" t="inlineStr">
+      <c r="S4" s="8" t="inlineStr">
         <is>
           <t>Equity Long/Short</t>
         </is>
       </c>
-      <c r="S4" s="8" t="inlineStr">
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>Hedge Funds</t>
         </is>
@@ -2975,50 +3515,55 @@
       </c>
       <c r="E5" s="8" t="inlineStr">
         <is>
+          <t>ex-HFs</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
           <t>Irish Onshore</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Public Equity</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="H5" s="8" t="inlineStr">
         <is>
           <t>Alternatives</t>
         </is>
       </c>
-      <c r="L5" s="8" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>PMG Floor</t>
         </is>
       </c>
-      <c r="M5" s="8" t="inlineStr">
+      <c r="N5" s="8" t="inlineStr">
         <is>
           <t>USD|Equity Not Hedged</t>
         </is>
       </c>
-      <c r="N5" s="8" t="inlineStr">
+      <c r="O5" s="8" t="inlineStr">
         <is>
           <t>FRUS1VA</t>
         </is>
       </c>
-      <c r="O5" s="8" t="inlineStr">
+      <c r="P5" s="8" t="inlineStr">
         <is>
           <t>US Large Cap Value Equity</t>
         </is>
       </c>
-      <c r="Q5" s="8" t="inlineStr">
+      <c r="R5" s="8" t="inlineStr">
         <is>
           <t>FRUS1GR</t>
         </is>
       </c>
-      <c r="R5" s="8" t="inlineStr">
+      <c r="S5" s="8" t="inlineStr">
         <is>
           <t>US Large Cap Growth Equity</t>
         </is>
       </c>
-      <c r="S5" s="8" t="inlineStr">
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>Public Equity</t>
         </is>
@@ -3030,47 +3575,52 @@
           <t>ModAgg</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>Hedge Funds</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="H6" s="8" t="inlineStr">
         <is>
           <t>Asset Allocation</t>
         </is>
       </c>
-      <c r="L6" s="8" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>PMG Target</t>
         </is>
       </c>
-      <c r="M6" s="8" t="inlineStr">
+      <c r="N6" s="8" t="inlineStr">
         <is>
           <t>GBP|Hedged</t>
         </is>
       </c>
-      <c r="N6" s="8" t="inlineStr">
+      <c r="O6" s="8" t="inlineStr">
         <is>
           <t>FRUSS2L</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="P6" s="8" t="inlineStr">
         <is>
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="R6" s="8" t="inlineStr">
         <is>
           <t>FRUS1VA</t>
         </is>
       </c>
-      <c r="R6" s="8" t="inlineStr">
+      <c r="S6" s="8" t="inlineStr">
         <is>
           <t>US Large Cap Value Equity</t>
         </is>
       </c>
-      <c r="S6" s="8" t="inlineStr">
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>Public Equity</t>
         </is>
@@ -3082,42 +3632,42 @@
           <t>Agg</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>Private Equity &amp; Other Private Assets</t>
         </is>
       </c>
-      <c r="L7" s="8" t="inlineStr">
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>PMG Ceiling</t>
         </is>
       </c>
-      <c r="M7" s="8" t="inlineStr">
+      <c r="N7" s="8" t="inlineStr">
         <is>
           <t>GBP|ISG Hedged</t>
         </is>
       </c>
-      <c r="N7" s="8" t="inlineStr">
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>MSEXUKL</t>
         </is>
       </c>
-      <c r="O7" s="8" t="inlineStr">
+      <c r="P7" s="8" t="inlineStr">
         <is>
           <t>Europe ex-UK Equity</t>
         </is>
       </c>
-      <c r="Q7" s="8" t="inlineStr">
+      <c r="R7" s="8" t="inlineStr">
         <is>
           <t>FRUSS2L</t>
         </is>
       </c>
-      <c r="R7" s="8" t="inlineStr">
+      <c r="S7" s="8" t="inlineStr">
         <is>
           <t>US Small Cap Equity</t>
         </is>
       </c>
-      <c r="S7" s="8" t="inlineStr">
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>Public Equity</t>
         </is>
@@ -3129,37 +3679,37 @@
           <t>Higher Risk</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>Asset Allocation Strategies</t>
         </is>
       </c>
-      <c r="M8" s="8" t="inlineStr">
+      <c r="N8" s="8" t="inlineStr">
         <is>
           <t>GBP|Unhedged</t>
         </is>
       </c>
-      <c r="N8" s="8" t="inlineStr">
+      <c r="O8" s="8" t="inlineStr">
         <is>
           <t>MSUTDKL</t>
         </is>
       </c>
-      <c r="O8" s="8" t="inlineStr">
+      <c r="P8" s="8" t="inlineStr">
         <is>
           <t>UK Equity</t>
         </is>
       </c>
-      <c r="Q8" s="8" t="inlineStr">
+      <c r="R8" s="8" t="inlineStr">
         <is>
           <t>LHTRYIN</t>
         </is>
       </c>
-      <c r="R8" s="8" t="inlineStr">
+      <c r="S8" s="8" t="inlineStr">
         <is>
           <t>US Dollar Debt</t>
         </is>
       </c>
-      <c r="S8" s="8" t="inlineStr">
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>Investment Grade Fixed Income</t>
         </is>
@@ -3171,369 +3721,369 @@
           <t>All Equity</t>
         </is>
       </c>
-      <c r="M9" s="8" t="inlineStr">
+      <c r="N9" s="8" t="inlineStr">
         <is>
           <t>GBP|Equity Not Hedged</t>
         </is>
       </c>
-      <c r="N9" s="8" t="inlineStr">
+      <c r="O9" s="8" t="inlineStr">
         <is>
           <t>MSJPANL</t>
         </is>
       </c>
-      <c r="O9" s="8" t="inlineStr">
+      <c r="P9" s="8" t="inlineStr">
         <is>
           <t>Japanese Equity</t>
         </is>
       </c>
-      <c r="Q9" s="8" t="inlineStr">
+      <c r="R9" s="8" t="inlineStr">
         <is>
           <t>LHUT1T3</t>
         </is>
       </c>
-      <c r="R9" s="8" t="inlineStr">
+      <c r="S9" s="8" t="inlineStr">
         <is>
           <t>Tactical Tilt Fund</t>
         </is>
       </c>
-      <c r="S9" s="8" t="inlineStr">
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>Asset Allocation Strategies</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="M10" s="8" t="inlineStr">
+      <c r="N10" s="8" t="inlineStr">
         <is>
           <t>CHF|Hedged</t>
         </is>
       </c>
-      <c r="N10" s="8" t="inlineStr">
+      <c r="O10" s="8" t="inlineStr">
         <is>
           <t>MSPXJPL</t>
         </is>
       </c>
-      <c r="O10" s="8" t="inlineStr">
+      <c r="P10" s="8" t="inlineStr">
         <is>
           <t>Asia-Pacific Equity</t>
         </is>
       </c>
-      <c r="Q10" s="8" t="inlineStr">
+      <c r="R10" s="8" t="inlineStr">
         <is>
           <t>LHYIELD</t>
         </is>
       </c>
-      <c r="R10" s="8" t="inlineStr">
+      <c r="S10" s="8" t="inlineStr">
         <is>
           <t>US High Yield</t>
         </is>
       </c>
-      <c r="S10" s="8" t="inlineStr">
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>Other Fixed Income</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="M11" s="8" t="inlineStr">
+      <c r="N11" s="8" t="inlineStr">
         <is>
           <t>CHF|ISG Hedged</t>
         </is>
       </c>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="O11" s="8" t="inlineStr">
         <is>
           <t>MSEMKF$</t>
         </is>
       </c>
-      <c r="O11" s="8" t="inlineStr">
+      <c r="P11" s="8" t="inlineStr">
         <is>
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="Q11" s="8" t="inlineStr">
+      <c r="R11" s="8" t="inlineStr">
         <is>
           <t>MSEMKF$</t>
         </is>
       </c>
-      <c r="R11" s="8" t="inlineStr">
+      <c r="S11" s="8" t="inlineStr">
         <is>
           <t>Emerging Market Equity</t>
         </is>
       </c>
-      <c r="S11" s="8" t="inlineStr">
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>Public Equity</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="M12" s="8" t="inlineStr">
+      <c r="N12" s="8" t="inlineStr">
         <is>
           <t>CHF|Unhedged</t>
         </is>
       </c>
-      <c r="N12" s="8" t="inlineStr">
+      <c r="O12" s="8" t="inlineStr">
         <is>
           <t>CSTEVDH</t>
         </is>
       </c>
-      <c r="O12" s="8" t="inlineStr">
+      <c r="P12" s="8" t="inlineStr">
         <is>
           <t>Event Driven</t>
         </is>
       </c>
-      <c r="Q12" s="8" t="inlineStr">
+      <c r="R12" s="8" t="inlineStr">
         <is>
           <t>MSEXUKL</t>
         </is>
       </c>
-      <c r="R12" s="8" t="inlineStr">
+      <c r="S12" s="8" t="inlineStr">
         <is>
           <t>Europe ex-UK Equity</t>
         </is>
       </c>
-      <c r="S12" s="8" t="inlineStr">
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>Public Equity</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="M13" s="8" t="inlineStr">
+      <c r="N13" s="8" t="inlineStr">
         <is>
           <t>CHF|Equity Not Hedged</t>
         </is>
       </c>
-      <c r="N13" s="8" t="inlineStr">
+      <c r="O13" s="8" t="inlineStr">
         <is>
           <t>CSTLNSH</t>
         </is>
       </c>
-      <c r="O13" s="8" t="inlineStr">
+      <c r="P13" s="8" t="inlineStr">
         <is>
           <t>Equity Long/Short</t>
         </is>
       </c>
-      <c r="Q13" s="8" t="inlineStr">
+      <c r="R13" s="8" t="inlineStr">
         <is>
           <t>MSJPANL</t>
         </is>
       </c>
-      <c r="R13" s="8" t="inlineStr">
+      <c r="S13" s="8" t="inlineStr">
         <is>
           <t>Japanese Equity</t>
         </is>
       </c>
-      <c r="S13" s="8" t="inlineStr">
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>Public Equity</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="M14" s="8" t="inlineStr">
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t>EUR|Hedged</t>
         </is>
       </c>
-      <c r="N14" s="8" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>CSFBMTT</t>
         </is>
       </c>
-      <c r="O14" s="8" t="inlineStr">
+      <c r="P14" s="8" t="inlineStr">
         <is>
           <t>Tactical Trading</t>
         </is>
       </c>
-      <c r="Q14" s="8" t="inlineStr">
+      <c r="R14" s="8" t="inlineStr">
         <is>
           <t>MSPXJPL</t>
         </is>
       </c>
-      <c r="R14" s="8" t="inlineStr">
+      <c r="S14" s="8" t="inlineStr">
         <is>
           <t>Asia-Pacific Equity</t>
         </is>
       </c>
-      <c r="S14" s="8" t="inlineStr">
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>Public Equity</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="M15" s="8" t="inlineStr">
+      <c r="N15" s="8" t="inlineStr">
         <is>
           <t>EUR|ISG Hedged</t>
         </is>
       </c>
-      <c r="N15" s="8" t="inlineStr">
+      <c r="O15" s="8" t="inlineStr">
         <is>
           <t>PE_BUYOUT</t>
         </is>
       </c>
-      <c r="O15" s="8" t="inlineStr">
+      <c r="P15" s="8" t="inlineStr">
         <is>
           <t>Buyout</t>
         </is>
       </c>
-      <c r="Q15" s="8" t="inlineStr">
+      <c r="R15" s="8" t="inlineStr">
         <is>
           <t>MSUTDKL</t>
         </is>
       </c>
-      <c r="R15" s="8" t="inlineStr">
+      <c r="S15" s="8" t="inlineStr">
         <is>
           <t>UK Equity</t>
         </is>
       </c>
-      <c r="S15" s="8" t="inlineStr">
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>Public Equity</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="M16" s="8" t="inlineStr">
+      <c r="N16" s="8" t="inlineStr">
         <is>
           <t>EUR|Unhedged</t>
         </is>
       </c>
-      <c r="N16" s="8" t="inlineStr">
+      <c r="O16" s="8" t="inlineStr">
         <is>
           <t>PE_GROWTH</t>
         </is>
       </c>
-      <c r="O16" s="8" t="inlineStr">
+      <c r="P16" s="8" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="Q16" s="8" t="inlineStr">
+      <c r="R16" s="8" t="inlineStr">
         <is>
           <t>PA_REAL_ESTATE</t>
         </is>
       </c>
-      <c r="R16" s="8" t="inlineStr">
+      <c r="S16" s="8" t="inlineStr">
         <is>
           <t>Core Real Estate</t>
         </is>
       </c>
-      <c r="S16" s="8" t="inlineStr">
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>Other Private Assets</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="M17" s="8" t="inlineStr">
+      <c r="N17" s="8" t="inlineStr">
         <is>
           <t>EUR|Equity Not Hedged</t>
         </is>
       </c>
-      <c r="N17" s="8" t="inlineStr">
+      <c r="O17" s="8" t="inlineStr">
         <is>
           <t>PE_VENTURE</t>
         </is>
       </c>
-      <c r="O17" s="8" t="inlineStr">
+      <c r="P17" s="8" t="inlineStr">
         <is>
           <t>Venture</t>
         </is>
       </c>
-      <c r="Q17" s="8" t="inlineStr">
+      <c r="R17" s="8" t="inlineStr">
         <is>
           <t>PE_BUYOUT</t>
         </is>
       </c>
-      <c r="R17" s="8" t="inlineStr">
+      <c r="S17" s="8" t="inlineStr">
         <is>
           <t>Buyout</t>
         </is>
       </c>
-      <c r="S17" s="8" t="inlineStr">
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>Private Equity</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="N18" s="8" t="inlineStr">
+      <c r="O18" s="8" t="inlineStr">
         <is>
           <t>PRIVATE_CREDIT</t>
         </is>
       </c>
-      <c r="O18" s="8" t="inlineStr">
+      <c r="P18" s="8" t="inlineStr">
         <is>
           <t>Private Credit</t>
         </is>
       </c>
-      <c r="Q18" s="8" t="inlineStr">
+      <c r="R18" s="8" t="inlineStr">
         <is>
           <t>PE_GROWTH</t>
         </is>
       </c>
-      <c r="R18" s="8" t="inlineStr">
+      <c r="S18" s="8" t="inlineStr">
         <is>
           <t>Growth</t>
         </is>
       </c>
-      <c r="S18" s="8" t="inlineStr">
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>Private Equity</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="N19" s="8" t="inlineStr">
+      <c r="O19" s="8" t="inlineStr">
         <is>
           <t>PA_REAL_ESTATE</t>
         </is>
       </c>
-      <c r="O19" s="8" t="inlineStr">
+      <c r="P19" s="8" t="inlineStr">
         <is>
           <t>Core Real Estate</t>
         </is>
       </c>
-      <c r="Q19" s="8" t="inlineStr">
+      <c r="R19" s="8" t="inlineStr">
         <is>
           <t>PE_VENTURE</t>
         </is>
       </c>
-      <c r="R19" s="8" t="inlineStr">
+      <c r="S19" s="8" t="inlineStr">
         <is>
           <t>Venture</t>
         </is>
       </c>
-      <c r="S19" s="8" t="inlineStr">
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>Private Equity</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="N20" s="8" t="inlineStr">
+      <c r="O20" s="8" t="inlineStr">
         <is>
           <t>LHUT1T3</t>
         </is>
       </c>
-      <c r="O20" s="8" t="inlineStr">
+      <c r="P20" s="8" t="inlineStr">
         <is>
           <t>Tactical Tilt Fund</t>
         </is>
       </c>
-      <c r="Q20" s="8" t="inlineStr">
+      <c r="R20" s="8" t="inlineStr">
         <is>
           <t>PRIVATE_CREDIT</t>
         </is>
       </c>
-      <c r="R20" s="8" t="inlineStr">
+      <c r="S20" s="8" t="inlineStr">
         <is>
           <t>Private Credit</t>
         </is>
       </c>
-      <c r="S20" s="8" t="inlineStr">
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>Other Private Assets</t>
         </is>
@@ -3609,7 +4159,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="B2:B5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
-      <formula1>'Valid values'!$N$2:$N$20</formula1>
+      <formula1>'Valid values'!$O$2:$O$20</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3842,10 +4392,10 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="L2:L5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
-      <formula1>'Valid values'!$G$2:$G$6</formula1>
+      <formula1>'Valid values'!$H$2:$H$6</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
-      <formula1>'Valid values'!$H$2:$H$3</formula1>
+      <formula1>'Valid values'!$I$2:$I$3</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3860,14 +4410,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3888,10 +4439,15 @@
       </c>
       <c r="D1" s="4" t="inlineStr">
         <is>
+          <t>Edition</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
           <t>ProductId</t>
         </is>
       </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
@@ -3913,12 +4469,13 @@
           <t>SMA Only</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
+      <c r="D2" s="3" t="n"/>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>gsam-core-municipal-sma</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -3938,22 +4495,113 @@
           <t>SMA Only</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="3" t="n"/>
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>gsam-intermediate-credit-sma</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.35</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>PMG Multi-Asset Portfolio</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Investment Grade Fixed Income</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>SMA Only</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>gsam-core-municipal-sma</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>PMG Multi-Asset Portfolio</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Investment Grade Fixed Income</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>SMA Only</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>gsam-intermediate-credit-sma</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>PMG Multi-Asset Portfolio</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Investment Grade Fixed Income</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>SMA Only</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>EUR Mod / GBP Full</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>gsam-intermediate-credit-sma</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="A2:A5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
-      <formula1>'Valid values'!$E$2:$E$5</formula1>
+      <formula1>'Valid values'!$F$2:$F$5</formula1>
     </dataValidation>
     <dataValidation sqref="B2:B5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
-      <formula1>'Valid values'!$F$2:$F$8</formula1>
+      <formula1>'Valid values'!$G$2:$G$8</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3962,6 +4610,175 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00A64D1E"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Variant</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Sleeve</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Edition</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>RiskLevel</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>AllocationType</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>PMG Multi-Asset Portfolio</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Investment Grade Fixed Income</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>SMA Only</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="n"/>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Full|Core|ex-HFs|NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>PMG Multi-Asset Portfolio</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Investment Grade Fixed Income</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>SMA Only</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>EUR Mod / GBP Full</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>PMG Multi-Asset Portfolio</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Investment Grade Fixed Income</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>SMA Only</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>EUR Mod / GBP Full</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>GBP</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="n"/>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Full</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="2">
+    <dataValidation sqref="A2:A5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
+      <formula1>'Valid values'!$F$2:$F$5</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
+      <formula1>'Valid values'!$G$2:$G$8</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00B42318"/>
@@ -4088,16 +4905,16 @@
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="A2:A5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
-      <formula1>'Valid values'!$I$2:$I$3</formula1>
+      <formula1>'Valid values'!$J$2:$J$3</formula1>
     </dataValidation>
     <dataValidation sqref="B2:B5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
-      <formula1>'Valid values'!$G$2:$G$6</formula1>
+      <formula1>'Valid values'!$H$2:$H$6</formula1>
     </dataValidation>
     <dataValidation sqref="F2:F5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
-      <formula1>'Valid values'!$J$2:$J$3</formula1>
+      <formula1>'Valid values'!$K$2:$K$3</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
-      <formula1>'Valid values'!$K$2:$K$4</formula1>
+      <formula1>'Valid values'!$L$2:$L$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4105,7 +4922,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="005B6B7C"/>
@@ -4159,216 +4976,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="008A6D1B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="17" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Slice</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>AnalyticsCurrency</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>ReportingName</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Lower</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Mean</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Upper</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Volatility</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>Sharpe</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>TotalReturn</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>HedgingRatio</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>From</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>To</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>USD|Hedged</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>US Dollar Debt</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Investment Grade Fixed Income</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0.005996386355446893</v>
-      </c>
-      <c r="F2" s="3" t="n">
-        <v>0.01114331525420141</v>
-      </c>
-      <c r="G2" s="3" t="n">
-        <v>0.01629024415295593</v>
-      </c>
-      <c r="H2" s="3" t="n">
-        <v>0.03218769340281281</v>
-      </c>
-      <c r="I2" s="3" t="n">
-        <v>0.3461980053913284</v>
-      </c>
-      <c r="J2" s="3" t="n">
-        <v>0.03614331525420142</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L2" s="3" t="inlineStr">
-        <is>
-          <t>1973-02-28</t>
-        </is>
-      </c>
-      <c r="M2" s="3" t="inlineStr">
-        <is>
-          <t>2025-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>USD|Hedged</t>
-        </is>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>US High Yield</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Other Fixed Income</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0.0169879773721</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0.03012601151314502</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>0.04326404565419004</v>
-      </c>
-      <c r="H3" s="3" t="n">
-        <v>0.0821622025806448</v>
-      </c>
-      <c r="I3" s="3" t="n">
-        <v>0.3666650913304739</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>0.05512601151314502</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>1983-08-31</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>2025-04-30</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="2">
-    <dataValidation sqref="A2:A5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
-      <formula1>'Valid values'!$M$2:$M$17</formula1>
-    </dataValidation>
-    <dataValidation sqref="C2:C5000" showErrorMessage="1" showDropDown="0" showInputMessage="1" allowBlank="1" errorTitle="Not a permitted value" error="Choose a value from the Valid values sheet." type="list">
-      <formula1>'Valid values'!$O$2:$O$20</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
-</worksheet>
 </file>